--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486869_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486869_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.0564</v>
+        <v>9.055400000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>8.323700000000001</v>
+        <v>9.055999999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.2674</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="G2" t="n">
         <v>9.6568</v>
@@ -610,13 +610,13 @@
         <v>1.6427</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.0542</v>
+        <v>-0.0552</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.9804</v>
+        <v>-0.2481</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.0738</v>
+        <v>0.1929</v>
       </c>
       <c r="V2" t="n">
         <v>0.0698</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. TEJERA TEJO</t>
+          <t>M. ABDULSALAM</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.066</v>
+        <v>0.9429</v>
       </c>
       <c r="E3" t="n">
-        <v>2.217</v>
+        <v>1.1903</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.151</v>
+        <v>-0.2473</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.2211</v>
+        <v>0.0041</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.4896</v>
+        <v>-0.1331</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2686</v>
+        <v>0.1372</v>
       </c>
       <c r="J3" t="n">
-        <v>0.6519</v>
+        <v>2.1079</v>
       </c>
       <c r="K3" t="n">
-        <v>0.4545</v>
+        <v>1.95</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1973</v>
+        <v>0.1579</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.8729</v>
+        <v>-2.1038</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.9442</v>
+        <v>-2.083</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0713</v>
+        <v>-0.0207</v>
       </c>
       <c r="P3" t="n">
-        <v>0.4107</v>
+        <v>-0.8214</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-2.0534</v>
       </c>
       <c r="R3" t="n">
-        <v>0.4107</v>
+        <v>1.2321</v>
       </c>
       <c r="S3" t="n">
-        <v>1.8065</v>
+        <v>0.2325</v>
       </c>
       <c r="T3" t="n">
-        <v>1.5651</v>
+        <v>-0.0428</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2414</v>
+        <v>0.2753</v>
       </c>
       <c r="V3" t="n">
-        <v>0.0698</v>
+        <v>1.5277</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.1786</v>
       </c>
       <c r="X3" t="n">
-        <v>0.0698</v>
+        <v>0.3491</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M. ABDULSALAM</t>
+          <t>J. TEJERA TEJO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.9402</v>
+        <v>0.8997000000000001</v>
       </c>
       <c r="E4" t="n">
-        <v>1.7133</v>
+        <v>0.9617</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2269</v>
+        <v>-0.0621</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0041</v>
+        <v>-0.2211</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.1331</v>
+        <v>-0.4896</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1372</v>
+        <v>0.2686</v>
       </c>
       <c r="J4" t="n">
-        <v>2.1079</v>
+        <v>0.6519</v>
       </c>
       <c r="K4" t="n">
-        <v>1.95</v>
+        <v>0.4545</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1579</v>
+        <v>0.1973</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.1038</v>
+        <v>-0.8729</v>
       </c>
       <c r="N4" t="n">
-        <v>-2.083</v>
+        <v>-0.9442</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.0207</v>
+        <v>0.0713</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.8214</v>
+        <v>0.4107</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.0534</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.2321</v>
+        <v>0.4107</v>
       </c>
       <c r="S4" t="n">
-        <v>1.2298</v>
+        <v>0.6402</v>
       </c>
       <c r="T4" t="n">
-        <v>0.4802</v>
+        <v>0.3098</v>
       </c>
       <c r="U4" t="n">
-        <v>0.7496</v>
+        <v>0.3304</v>
       </c>
       <c r="V4" t="n">
-        <v>1.5277</v>
+        <v>0.0698</v>
       </c>
       <c r="W4" t="n">
-        <v>1.1786</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0.3491</v>
+        <v>0.0698</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>W. CABRAL BUERIBERI</t>
+          <t>C. HENDERSON</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.4141</v>
+        <v>0.2002</v>
       </c>
       <c r="E5" t="n">
-        <v>0.4165</v>
+        <v>0.8208</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.0024</v>
+        <v>-0.6206</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.536</v>
+        <v>0.1392</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.9861</v>
+        <v>0.889</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.5498</v>
+        <v>-0.7498</v>
       </c>
       <c r="J5" t="n">
-        <v>0.2574</v>
+        <v>0.786</v>
       </c>
       <c r="K5" t="n">
-        <v>0.9023</v>
+        <v>1.4439</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.6449</v>
+        <v>-0.6579</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.7934</v>
+        <v>-0.6468</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.8884</v>
+        <v>-0.5548999999999999</v>
       </c>
       <c r="O5" t="n">
-        <v>0.095</v>
+        <v>-0.092</v>
       </c>
       <c r="P5" t="n">
-        <v>1.0267</v>
+        <v>0.616</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.2053</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.2321</v>
+        <v>0.616</v>
       </c>
       <c r="S5" t="n">
-        <v>0.9233</v>
+        <v>-0.1443</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.2249</v>
+        <v>0.0348</v>
       </c>
       <c r="U5" t="n">
-        <v>1.1482</v>
+        <v>-0.1791</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>-0.4107</v>
       </c>
       <c r="W5" t="n">
-        <v>0.5893</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.5893</v>
+        <v>-0.4107</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>C. HENDERSON</t>
+          <t>W. CABRAL BUERIBERI</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3797</v>
+        <v>-0.1286</v>
       </c>
       <c r="E6" t="n">
-        <v>1.03</v>
+        <v>0.3778</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.6502</v>
+        <v>-0.5064</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1392</v>
+        <v>-1.536</v>
       </c>
       <c r="H6" t="n">
-        <v>0.889</v>
+        <v>-0.9861</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.7498</v>
+        <v>-0.5498</v>
       </c>
       <c r="J6" t="n">
-        <v>0.786</v>
+        <v>0.2574</v>
       </c>
       <c r="K6" t="n">
-        <v>1.4439</v>
+        <v>0.9023</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.6579</v>
+        <v>-0.6449</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.6468</v>
+        <v>-1.7934</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.5548999999999999</v>
+        <v>-1.8884</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.092</v>
+        <v>0.095</v>
       </c>
       <c r="P6" t="n">
-        <v>0.616</v>
+        <v>1.0267</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-0.2053</v>
       </c>
       <c r="R6" t="n">
-        <v>0.616</v>
+        <v>1.2321</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0352</v>
+        <v>0.3807</v>
       </c>
       <c r="T6" t="n">
-        <v>0.244</v>
+        <v>-0.2636</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2088</v>
+        <v>0.6443</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.4107</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>0.5893</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.4107</v>
+        <v>-0.5893</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. AKINWOLE</t>
+          <t>I. IBAÑEZ ZAMALLOA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.4024</v>
+        <v>-1.0288</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.9519</v>
+        <v>-0.8045</v>
       </c>
       <c r="F7" t="n">
-        <v>0.5496</v>
+        <v>-0.2242</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.7863</v>
+        <v>-1.3213</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.7074</v>
+        <v>-1.2293</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.0789</v>
+        <v>-0.092</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.003</v>
+        <v>0.0015</v>
       </c>
       <c r="K7" t="n">
-        <v>0.6813</v>
+        <v>-0.0905</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.6843</v>
+        <v>0.092</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.7833</v>
+        <v>-1.3228</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.3887</v>
+        <v>-1.1389</v>
       </c>
       <c r="O7" t="n">
-        <v>0.6054</v>
+        <v>-0.1839</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.4107</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.2321</v>
+        <v>-1.0267</v>
       </c>
       <c r="R7" t="n">
-        <v>0.8214</v>
+        <v>1.0267</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.2053</v>
+        <v>0.2227</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.7169</v>
+        <v>0.2207</v>
       </c>
       <c r="U7" t="n">
-        <v>0.5115</v>
+        <v>0.002</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.0698</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>0.0698</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>I. IBAÑEZ ZAMALLOA</t>
+          <t>A. AKINWOLE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.639</v>
+        <v>-1.2319</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.1184</v>
+        <v>-1.7815</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.5206</v>
+        <v>0.5496</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.3213</v>
+        <v>-0.7863</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.2293</v>
+        <v>-0.7074</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.092</v>
+        <v>-0.0789</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0015</v>
+        <v>-0.003</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.0905</v>
+        <v>0.6813</v>
       </c>
       <c r="L8" t="n">
-        <v>0.092</v>
+        <v>-0.6843</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.3228</v>
+        <v>-0.7833</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.1389</v>
+        <v>-1.3887</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.1839</v>
+        <v>0.6054</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>-0.4107</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.0267</v>
+        <v>-1.2321</v>
       </c>
       <c r="R8" t="n">
-        <v>1.0267</v>
+        <v>0.8214</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.3875</v>
+        <v>-0.0349</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.0931</v>
+        <v>-0.5464</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2944</v>
+        <v>0.5115</v>
       </c>
       <c r="V8" t="n">
-        <v>0.0698</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0.0698</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.7813</v>
+        <v>-2.1331</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.0226</v>
+        <v>-2.4337</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2413</v>
+        <v>0.3006</v>
       </c>
       <c r="G9" t="n">
         <v>-3.7197</v>
@@ -1156,13 +1156,13 @@
         <v>1.0267</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.3634</v>
+        <v>0.2847</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.7246</v>
+        <v>-0.1357</v>
       </c>
       <c r="U9" t="n">
-        <v>0.3612</v>
+        <v>0.4204</v>
       </c>
       <c r="V9" t="n">
         <v>0.4805</v>
@@ -1189,10 +1189,10 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.1181</v>
+        <v>-3.7384</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.8898</v>
+        <v>-3.5101</v>
       </c>
       <c r="F10" t="n">
         <v>-0.2284</v>
@@ -1234,10 +1234,10 @@
         <v>0.616</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.6083</v>
+        <v>-0.2286</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.7905</v>
+        <v>-0.4108</v>
       </c>
       <c r="U10" t="n">
         <v>0.1822</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.3453</v>
+        <v>-4.2951</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.1386</v>
+        <v>-2.1773</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.2067</v>
+        <v>-2.1178</v>
       </c>
       <c r="G11" t="n">
         <v>-3.0749</v>
@@ -1312,13 +1312,13 @@
         <v>1.4374</v>
       </c>
       <c r="S11" t="n">
-        <v>0.4196</v>
+        <v>0.4697</v>
       </c>
       <c r="T11" t="n">
-        <v>0.4066</v>
+        <v>0.3679</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0129</v>
+        <v>0.1019</v>
       </c>
       <c r="V11" t="n">
         <v>-0.8686</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.9839</v>
+        <v>-4.6265</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.1148</v>
+        <v>-2.9056</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.8691</v>
+        <v>-1.7209</v>
       </c>
       <c r="G12" t="n">
         <v>-3.1912</v>
@@ -1390,13 +1390,13 @@
         <v>1.2321</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.0596</v>
+        <v>-0.7022</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.0462</v>
+        <v>-0.837</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.0134</v>
+        <v>0.1348</v>
       </c>
       <c r="V12" t="n">
         <v>-0.9384</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-6.413600000000002</v>
+        <v>-6.084199999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.535599999999999</v>
+        <v>-1.2061</v>
       </c>
       <c r="F13" t="n">
-        <v>-4.878</v>
+        <v>-4.8781</v>
       </c>
       <c r="G13" t="n">
         <v>-7.4986</v>
@@ -1438,13 +1438,13 @@
         <v>-10.8665</v>
       </c>
       <c r="I13" t="n">
-        <v>3.3681</v>
+        <v>3.368100000000001</v>
       </c>
       <c r="J13" t="n">
         <v>8.9101</v>
       </c>
       <c r="K13" t="n">
-        <v>5.7948</v>
+        <v>5.794799999999999</v>
       </c>
       <c r="L13" t="n">
         <v>3.1152</v>
@@ -1468,10 +1468,10 @@
         <v>11.2939</v>
       </c>
       <c r="S13" t="n">
-        <v>0.7361</v>
+        <v>1.0653</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.8807</v>
+        <v>-1.5512</v>
       </c>
       <c r="U13" t="n">
         <v>2.6166</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.99</v>
+        <v>5.438</v>
       </c>
       <c r="E14" t="n">
-        <v>2.3755</v>
+        <v>2.7939</v>
       </c>
       <c r="F14" t="n">
-        <v>2.6145</v>
+        <v>2.6441</v>
       </c>
       <c r="G14" t="n">
         <v>4.0201</v>
@@ -1546,13 +1546,13 @@
         <v>1.4374</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.6194</v>
+        <v>-0.1714</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.8563</v>
+        <v>-0.4379</v>
       </c>
       <c r="U14" t="n">
-        <v>0.2369</v>
+        <v>0.2665</v>
       </c>
       <c r="V14" t="n">
         <v>1.1786</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.1445</v>
+        <v>2.2247</v>
       </c>
       <c r="E15" t="n">
         <v>1.0974</v>
       </c>
       <c r="F15" t="n">
-        <v>1.0471</v>
+        <v>1.1273</v>
       </c>
       <c r="G15" t="n">
         <v>2.1182</v>
@@ -1624,13 +1624,13 @@
         <v>0.616</v>
       </c>
       <c r="S15" t="n">
-        <v>0.437</v>
+        <v>0.5172</v>
       </c>
       <c r="T15" t="n">
         <v>-0.159</v>
       </c>
       <c r="U15" t="n">
-        <v>0.596</v>
+        <v>0.6762</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. FANER CATALA</t>
+          <t>F. STUTZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.3865</v>
+        <v>1.6848</v>
       </c>
       <c r="E16" t="n">
-        <v>0.4954</v>
+        <v>0.8821</v>
       </c>
       <c r="F16" t="n">
-        <v>0.891</v>
+        <v>0.8027</v>
       </c>
       <c r="G16" t="n">
-        <v>2.6142</v>
+        <v>1.9317</v>
       </c>
       <c r="H16" t="n">
-        <v>1.067</v>
+        <v>0.4056</v>
       </c>
       <c r="I16" t="n">
-        <v>1.5472</v>
+        <v>1.5261</v>
       </c>
       <c r="J16" t="n">
-        <v>2.7737</v>
+        <v>1.7962</v>
       </c>
       <c r="K16" t="n">
-        <v>1.0901</v>
+        <v>1.1782</v>
       </c>
       <c r="L16" t="n">
-        <v>1.6836</v>
+        <v>0.6181</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.1595</v>
+        <v>0.1355</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.0231</v>
+        <v>-0.7726</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.1364</v>
+        <v>0.9081</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.8214</v>
+        <v>0.616</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.0534</v>
+        <v>-1.0267</v>
       </c>
       <c r="R16" t="n">
-        <v>1.2321</v>
+        <v>1.6427</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.4064</v>
+        <v>0.3157</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.2249</v>
+        <v>-0.4768</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1815</v>
+        <v>0.7925</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>-1.1786</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>0.5893</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-1.7679</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>F. STUTZ</t>
+          <t>J. FANER CATALA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.1583</v>
+        <v>1.2069</v>
       </c>
       <c r="E17" t="n">
-        <v>0.6729000000000001</v>
+        <v>0.2862</v>
       </c>
       <c r="F17" t="n">
-        <v>0.4854</v>
+        <v>0.9207</v>
       </c>
       <c r="G17" t="n">
-        <v>1.9317</v>
+        <v>2.6142</v>
       </c>
       <c r="H17" t="n">
-        <v>0.4056</v>
+        <v>1.067</v>
       </c>
       <c r="I17" t="n">
-        <v>1.5261</v>
+        <v>1.5472</v>
       </c>
       <c r="J17" t="n">
-        <v>1.7962</v>
+        <v>2.7737</v>
       </c>
       <c r="K17" t="n">
-        <v>1.1782</v>
+        <v>1.0901</v>
       </c>
       <c r="L17" t="n">
-        <v>0.6181</v>
+        <v>1.6836</v>
       </c>
       <c r="M17" t="n">
-        <v>0.1355</v>
+        <v>-0.1595</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.7726</v>
+        <v>-0.0231</v>
       </c>
       <c r="O17" t="n">
-        <v>0.9081</v>
+        <v>-0.1364</v>
       </c>
       <c r="P17" t="n">
-        <v>0.616</v>
+        <v>-0.8214</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.0267</v>
+        <v>-2.0534</v>
       </c>
       <c r="R17" t="n">
-        <v>1.6427</v>
+        <v>1.2321</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.2108</v>
+        <v>-0.5859</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.6860000000000001</v>
+        <v>-0.4341</v>
       </c>
       <c r="U17" t="n">
-        <v>0.4752</v>
+        <v>-0.1519</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.1786</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>0.5893</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.7679</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.5324</v>
+        <v>0.4347</v>
       </c>
       <c r="E18" t="n">
         <v>1.6623</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.13</v>
+        <v>-1.2276</v>
       </c>
       <c r="G18" t="n">
         <v>0.7020999999999999</v>
@@ -1858,13 +1858,13 @@
         <v>0.8214</v>
       </c>
       <c r="S18" t="n">
-        <v>0.5161</v>
+        <v>0.4184</v>
       </c>
       <c r="T18" t="n">
         <v>-0.2249</v>
       </c>
       <c r="U18" t="n">
-        <v>0.7409</v>
+        <v>0.6433</v>
       </c>
       <c r="V18" t="n">
         <v>-0.4805</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.3606</v>
+        <v>0.4199</v>
       </c>
       <c r="E19" t="n">
         <v>0.6153999999999999</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.2548</v>
+        <v>-0.1955</v>
       </c>
       <c r="G19" t="n">
         <v>0.2552</v>
@@ -1936,13 +1936,13 @@
         <v>0.4107</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.3053</v>
+        <v>-0.246</v>
       </c>
       <c r="T19" t="n">
         <v>-0.0659</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2394</v>
+        <v>-0.1801</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.2564</v>
+        <v>0.0368</v>
       </c>
       <c r="E20" t="n">
-        <v>0.9955000000000001</v>
+        <v>0.5770999999999999</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.7391</v>
+        <v>-0.5403</v>
       </c>
       <c r="G20" t="n">
         <v>-2.3479</v>
@@ -2014,13 +2014,13 @@
         <v>1.6427</v>
       </c>
       <c r="S20" t="n">
-        <v>0.4811</v>
+        <v>0.2615</v>
       </c>
       <c r="T20" t="n">
-        <v>0.3408</v>
+        <v>-0.07770000000000001</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1404</v>
+        <v>0.3391</v>
       </c>
       <c r="V20" t="n">
         <v>0.4805</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.0946</v>
+        <v>-0.051</v>
       </c>
       <c r="E21" t="n">
-        <v>0.4782</v>
+        <v>0.3736</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.5728</v>
+        <v>-0.4246</v>
       </c>
       <c r="G21" t="n">
         <v>2.5152</v>
@@ -2092,13 +2092,13 @@
         <v>1.6427</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.5831</v>
+        <v>-0.5395</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.2249</v>
+        <v>-0.3295</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3582</v>
+        <v>-0.21</v>
       </c>
       <c r="V21" t="n">
         <v>-0.5893</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.2248</v>
+        <v>-0.5682</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.783</v>
+        <v>-1.0969</v>
       </c>
       <c r="F22" t="n">
-        <v>0.5583</v>
+        <v>0.5286999999999999</v>
       </c>
       <c r="G22" t="n">
         <v>-1.2976</v>
@@ -2170,13 +2170,13 @@
         <v>0.616</v>
       </c>
       <c r="S22" t="n">
-        <v>0.4568</v>
+        <v>0.1133</v>
       </c>
       <c r="T22" t="n">
-        <v>0.1704</v>
+        <v>-0.1434</v>
       </c>
       <c r="U22" t="n">
-        <v>0.2864</v>
+        <v>0.2568</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.7199</v>
+        <v>-0.8779</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.0854</v>
+        <v>-1.3532</v>
       </c>
       <c r="F23" t="n">
-        <v>0.3654</v>
+        <v>0.4753</v>
       </c>
       <c r="G23" t="n">
         <v>-1.5337</v>
@@ -2248,13 +2248,13 @@
         <v>1.2321</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.872</v>
+        <v>-0.03</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.054</v>
+        <v>-0.3217</v>
       </c>
       <c r="U23" t="n">
-        <v>0.1819</v>
+        <v>0.2917</v>
       </c>
       <c r="V23" t="n">
         <v>0.4805</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.3758</v>
+        <v>-2.8378</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.6462</v>
+        <v>-0.96</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.7295</v>
+        <v>-1.8778</v>
       </c>
       <c r="G24" t="n">
         <v>-1.4788</v>
@@ -2326,13 +2326,13 @@
         <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>0.37</v>
+        <v>-0.092</v>
       </c>
       <c r="T24" t="n">
-        <v>0.368</v>
+        <v>0.0542</v>
       </c>
       <c r="U24" t="n">
-        <v>0.002</v>
+        <v>-0.1462</v>
       </c>
       <c r="V24" t="n">
         <v>-0.2402</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>6.413600000000001</v>
+        <v>7.110899999999999</v>
       </c>
       <c r="E25" t="n">
-        <v>4.878000000000001</v>
+        <v>4.8779</v>
       </c>
       <c r="F25" t="n">
-        <v>1.535500000000001</v>
+        <v>2.233</v>
       </c>
       <c r="G25" t="n">
         <v>7.498700000000003</v>
@@ -2404,13 +2404,13 @@
         <v>11.2938</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.7359999999999999</v>
+        <v>-0.03869999999999997</v>
       </c>
       <c r="T25" t="n">
         <v>-2.6167</v>
       </c>
       <c r="U25" t="n">
-        <v>1.8806</v>
+        <v>2.5779</v>
       </c>
       <c r="V25" t="n">
         <v>-0.3490000000000001</v>
